--- a/artfynd/A 14218-2021 artfynd.xlsx
+++ b/artfynd/A 14218-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125113713</v>
+        <v>125113777</v>
       </c>
       <c r="B2" t="n">
-        <v>57513</v>
+        <v>91705</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>67</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>454998</v>
+        <v>454984</v>
       </c>
       <c r="R2" t="n">
-        <v>6992039</v>
+        <v>6992080</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-05-15</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -889,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125113777</v>
+        <v>125113713</v>
       </c>
       <c r="B4" t="n">
-        <v>91705</v>
+        <v>57513</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -901,25 +896,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>67</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>454984</v>
+        <v>454998</v>
       </c>
       <c r="R4" t="n">
-        <v>6992080</v>
+        <v>6992039</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -965,6 +960,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 14218-2021 artfynd.xlsx
+++ b/artfynd/A 14218-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125113777</v>
+        <v>125113699</v>
       </c>
       <c r="B2" t="n">
-        <v>91705</v>
+        <v>91012</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>67</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>454984</v>
+        <v>455070</v>
       </c>
       <c r="R2" t="n">
-        <v>6992080</v>
+        <v>6991961</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -991,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125113699</v>
+        <v>125113777</v>
       </c>
       <c r="B5" t="n">
-        <v>91012</v>
+        <v>91705</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1003,25 +1003,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>67</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>455070</v>
+        <v>454984</v>
       </c>
       <c r="R5" t="n">
-        <v>6991961</v>
+        <v>6992080</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 14218-2021 artfynd.xlsx
+++ b/artfynd/A 14218-2021 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125113714</v>
+        <v>125113777</v>
       </c>
       <c r="B3" t="n">
-        <v>57513</v>
+        <v>91705</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>67</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>454920</v>
+        <v>454984</v>
       </c>
       <c r="R3" t="n">
-        <v>6992096</v>
+        <v>6992080</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -853,11 +853,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-05-15</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125113713</v>
+        <v>125113714</v>
       </c>
       <c r="B4" t="n">
         <v>57513</v>
@@ -924,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>454998</v>
+        <v>454920</v>
       </c>
       <c r="R4" t="n">
-        <v>6992039</v>
+        <v>6992096</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -991,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125113777</v>
+        <v>125113713</v>
       </c>
       <c r="B5" t="n">
-        <v>91705</v>
+        <v>57513</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1003,25 +998,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>67</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>454984</v>
+        <v>454998</v>
       </c>
       <c r="R5" t="n">
-        <v>6992080</v>
+        <v>6992039</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1067,6 +1062,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 14218-2021 artfynd.xlsx
+++ b/artfynd/A 14218-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125113699</v>
+        <v>125113777</v>
       </c>
       <c r="B2" t="n">
-        <v>91012</v>
+        <v>91705</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>67</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>455070</v>
+        <v>454984</v>
       </c>
       <c r="R2" t="n">
-        <v>6991961</v>
+        <v>6992080</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125113777</v>
+        <v>125113714</v>
       </c>
       <c r="B3" t="n">
-        <v>91705</v>
+        <v>57513</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>67</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>454984</v>
+        <v>454920</v>
       </c>
       <c r="R3" t="n">
-        <v>6992080</v>
+        <v>6992096</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -853,6 +853,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,7 +884,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125113714</v>
+        <v>125113713</v>
       </c>
       <c r="B4" t="n">
         <v>57513</v>
@@ -919,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>454920</v>
+        <v>454998</v>
       </c>
       <c r="R4" t="n">
-        <v>6992096</v>
+        <v>6992039</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125113713</v>
+        <v>125113699</v>
       </c>
       <c r="B5" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,21 +1007,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>454998</v>
+        <v>455070</v>
       </c>
       <c r="R5" t="n">
-        <v>6992039</v>
+        <v>6991961</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1062,11 +1067,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-05-15</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 14218-2021 artfynd.xlsx
+++ b/artfynd/A 14218-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125113777</v>
+        <v>125113713</v>
       </c>
       <c r="B2" t="n">
-        <v>91705</v>
+        <v>57513</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>67</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>454984</v>
+        <v>454998</v>
       </c>
       <c r="R2" t="n">
-        <v>6992080</v>
+        <v>6992039</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125113714</v>
+        <v>125113699</v>
       </c>
       <c r="B3" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>454920</v>
+        <v>455070</v>
       </c>
       <c r="R3" t="n">
-        <v>6992096</v>
+        <v>6991961</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -853,11 +858,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-05-15</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,7 +884,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125113713</v>
+        <v>125113714</v>
       </c>
       <c r="B4" t="n">
         <v>57513</v>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>454998</v>
+        <v>454920</v>
       </c>
       <c r="R4" t="n">
-        <v>6992039</v>
+        <v>6992096</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -991,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125113699</v>
+        <v>125113777</v>
       </c>
       <c r="B5" t="n">
-        <v>91012</v>
+        <v>91705</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1003,25 +1003,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>67</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>455070</v>
+        <v>454984</v>
       </c>
       <c r="R5" t="n">
-        <v>6991961</v>
+        <v>6992080</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 14218-2021 artfynd.xlsx
+++ b/artfynd/A 14218-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125113713</v>
+        <v>125113699</v>
       </c>
       <c r="B2" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>454998</v>
+        <v>455070</v>
       </c>
       <c r="R2" t="n">
-        <v>6992039</v>
+        <v>6991961</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-05-15</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125113699</v>
+        <v>125113714</v>
       </c>
       <c r="B3" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>455070</v>
+        <v>454920</v>
       </c>
       <c r="R3" t="n">
-        <v>6991961</v>
+        <v>6992096</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,6 +853,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,7 +884,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125113714</v>
+        <v>125113713</v>
       </c>
       <c r="B4" t="n">
         <v>57513</v>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>454920</v>
+        <v>454998</v>
       </c>
       <c r="R4" t="n">
-        <v>6992096</v>
+        <v>6992039</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 14218-2021 artfynd.xlsx
+++ b/artfynd/A 14218-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125113699</v>
+        <v>125113714</v>
       </c>
       <c r="B2" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>455070</v>
+        <v>454920</v>
       </c>
       <c r="R2" t="n">
-        <v>6991961</v>
+        <v>6992096</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125113714</v>
+        <v>125113777</v>
       </c>
       <c r="B3" t="n">
-        <v>57513</v>
+        <v>91705</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +794,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>67</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>454920</v>
+        <v>454984</v>
       </c>
       <c r="R3" t="n">
-        <v>6992096</v>
+        <v>6992080</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -853,11 +858,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-05-15</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125113713</v>
+        <v>125113699</v>
       </c>
       <c r="B4" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>454998</v>
+        <v>455070</v>
       </c>
       <c r="R4" t="n">
-        <v>6992039</v>
+        <v>6991961</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -960,11 +960,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-05-15</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125113777</v>
+        <v>125113713</v>
       </c>
       <c r="B5" t="n">
-        <v>91705</v>
+        <v>57513</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1003,25 +998,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>67</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>454984</v>
+        <v>454998</v>
       </c>
       <c r="R5" t="n">
-        <v>6992080</v>
+        <v>6992039</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1067,6 +1062,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 14218-2021 artfynd.xlsx
+++ b/artfynd/A 14218-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125113714</v>
+        <v>125113699</v>
       </c>
       <c r="B2" t="n">
-        <v>57513</v>
+        <v>91166</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>454920</v>
+        <v>455070</v>
       </c>
       <c r="R2" t="n">
-        <v>6992096</v>
+        <v>6991961</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-05-15</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125113777</v>
+        <v>125113714</v>
       </c>
       <c r="B3" t="n">
-        <v>91705</v>
+        <v>57635</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>67</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>454984</v>
+        <v>454920</v>
       </c>
       <c r="R3" t="n">
-        <v>6992080</v>
+        <v>6992096</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -858,6 +853,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125113699</v>
+        <v>125113713</v>
       </c>
       <c r="B4" t="n">
-        <v>91012</v>
+        <v>57635</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>455070</v>
+        <v>454998</v>
       </c>
       <c r="R4" t="n">
-        <v>6991961</v>
+        <v>6992039</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -960,6 +960,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-05-15</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -986,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125113713</v>
+        <v>125113777</v>
       </c>
       <c r="B5" t="n">
-        <v>57513</v>
+        <v>91865</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -998,25 +1003,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>67</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>454998</v>
+        <v>454984</v>
       </c>
       <c r="R5" t="n">
-        <v>6992039</v>
+        <v>6992080</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1062,11 +1067,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-05-15</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 14218-2021 artfynd.xlsx
+++ b/artfynd/A 14218-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125113699</v>
+        <v>125113777</v>
       </c>
       <c r="B2" t="n">
-        <v>91166</v>
+        <v>91865</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>67</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>455070</v>
+        <v>454984</v>
       </c>
       <c r="R2" t="n">
-        <v>6991961</v>
+        <v>6992080</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -991,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125113777</v>
+        <v>125113699</v>
       </c>
       <c r="B5" t="n">
-        <v>91865</v>
+        <v>91166</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1003,25 +1003,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>67</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>454984</v>
+        <v>455070</v>
       </c>
       <c r="R5" t="n">
-        <v>6992080</v>
+        <v>6991961</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 14218-2021 artfynd.xlsx
+++ b/artfynd/A 14218-2021 artfynd.xlsx
@@ -872,7 +872,7 @@
         <v>125113714</v>
       </c>
       <c r="B4" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>125113713</v>
       </c>
       <c r="B5" t="n">
-        <v>57651</v>
+        <v>57652</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 14218-2021 artfynd.xlsx
+++ b/artfynd/A 14218-2021 artfynd.xlsx
@@ -872,7 +872,7 @@
         <v>125113714</v>
       </c>
       <c r="B4" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>125113713</v>
       </c>
       <c r="B5" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 14218-2021 artfynd.xlsx
+++ b/artfynd/A 14218-2021 artfynd.xlsx
@@ -872,7 +872,7 @@
         <v>125113714</v>
       </c>
       <c r="B4" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>125113713</v>
       </c>
       <c r="B5" t="n">
-        <v>57656</v>
+        <v>57657</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
